--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HACHE PUBLICIDAD MORALEJA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HACHE PUBLICIDAD MORALEJA.xlsx
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1775</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2224</v>
+        <v>-0.1245</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3999</v>
+        <v>0.4245</v>
       </c>
       <c r="G5" t="n">
         <v>0.0305</v>
@@ -844,13 +844,13 @@
         <v>0.1853</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0383</v>
+        <v>0.0843</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U5" t="n">
-        <v>0.29</v>
+        <v>0.3146</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.370499999999998</v>
+        <v>-10.7549</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.462600000000002</v>
+        <v>-7.596800000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0925</v>
+        <v>-3.1583</v>
       </c>
       <c r="G7" t="n">
-        <v>-30.7639</v>
+        <v>-10.4881</v>
       </c>
       <c r="H7" t="n">
-        <v>-21.2554</v>
+        <v>6.3806</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.5085</v>
+        <v>-16.869</v>
       </c>
       <c r="J7" t="n">
-        <v>4.577799999999999</v>
+        <v>6.257499999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2609999999999999</v>
+        <v>16.5934</v>
       </c>
       <c r="L7" t="n">
-        <v>4.316800000000001</v>
+        <v>-10.3358</v>
       </c>
       <c r="M7" t="n">
-        <v>-35.342</v>
+        <v>-16.7454</v>
       </c>
       <c r="N7" t="n">
-        <v>-21.5166</v>
+        <v>-10.2126</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.8252</v>
+        <v>-6.5328</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.5586</v>
+        <v>-5.0028</v>
       </c>
       <c r="Q7" t="n">
-        <v>-56.5124</v>
+        <v>-31.3137</v>
       </c>
       <c r="R7" t="n">
-        <v>50.9541</v>
+        <v>26.3107</v>
       </c>
       <c r="S7" t="n">
-        <v>37.1191</v>
+        <v>-3.0696</v>
       </c>
       <c r="T7" t="n">
-        <v>24.5431</v>
+        <v>-3.6239</v>
       </c>
       <c r="U7" t="n">
-        <v>12.5759</v>
+        <v>0.5542000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.167</v>
+        <v>7.8057</v>
       </c>
       <c r="W7" t="n">
-        <v>17.9288</v>
+        <v>21.0834</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.0955</v>
+        <v>-13.2777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>J. CARO SERRANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>-20.4626</v>
+        <v>-18.1452</v>
       </c>
       <c r="E8" t="n">
-        <v>-15.3908</v>
+        <v>-10.5242</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.0722</v>
+        <v>-7.621</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.4881</v>
+        <v>-19.7849</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3806</v>
+        <v>-4.9733</v>
       </c>
       <c r="I8" t="n">
-        <v>-16.869</v>
+        <v>-14.8119</v>
       </c>
       <c r="J8" t="n">
-        <v>6.257499999999999</v>
+        <v>-9.2615</v>
       </c>
       <c r="K8" t="n">
-        <v>16.5934</v>
+        <v>-0.3394999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-10.3358</v>
+        <v>-8.9221</v>
       </c>
       <c r="M8" t="n">
-        <v>-16.7454</v>
+        <v>-10.5235</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.2126</v>
+        <v>-4.633599999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.5328</v>
+        <v>-5.889699999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.0028</v>
+        <v>4.4471</v>
       </c>
       <c r="Q8" t="n">
-        <v>-31.3137</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>26.3107</v>
+        <v>5.5588</v>
       </c>
       <c r="S8" t="n">
-        <v>-12.7773</v>
+        <v>-1.6135</v>
       </c>
       <c r="T8" t="n">
-        <v>-11.4177</v>
+        <v>-0.1509000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3595</v>
+        <v>-1.4627</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8057</v>
+        <v>-1.1937</v>
       </c>
       <c r="W8" t="n">
-        <v>21.0834</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.2777</v>
+        <v>-1.1937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CARO SERRANO</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-20.8199</v>
+        <v>-21.6499</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.7335</v>
+        <v>-21.6658</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.086500000000001</v>
+        <v>0.01580000000000048</v>
       </c>
       <c r="G9" t="n">
-        <v>-19.7849</v>
+        <v>-8.3469</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.9733</v>
+        <v>-11.0411</v>
       </c>
       <c r="I9" t="n">
-        <v>-14.8119</v>
+        <v>2.6939</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.2615</v>
+        <v>5.3044</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3394999999999999</v>
+        <v>-1.634500000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.9221</v>
+        <v>6.938800000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.5235</v>
+        <v>-13.6513</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.633599999999999</v>
+        <v>-9.4063</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.889699999999999</v>
+        <v>-4.245</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4471</v>
+        <v>-3.7056</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1117</v>
+        <v>-25.199</v>
       </c>
       <c r="R9" t="n">
-        <v>5.5588</v>
+        <v>21.4936</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.2882</v>
+        <v>-6.0097</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.3601</v>
+        <v>-3.6567</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.9281</v>
+        <v>-2.353</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1937</v>
+        <v>-3.5877</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8853</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1937</v>
+        <v>-5.473199999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>H. HERNANDEZ CASTANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>-22.1417</v>
+        <v>-23.9103</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.3882</v>
+        <v>-17.0267</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.7536</v>
+        <v>-6.8834</v>
       </c>
       <c r="G10" t="n">
-        <v>-35.3574</v>
+        <v>-10.9013</v>
       </c>
       <c r="H10" t="n">
-        <v>-20.1295</v>
+        <v>-7.2875</v>
       </c>
       <c r="I10" t="n">
-        <v>-15.2282</v>
+        <v>-3.6138</v>
       </c>
       <c r="J10" t="n">
-        <v>12.8279</v>
+        <v>-8.0885</v>
       </c>
       <c r="K10" t="n">
-        <v>4.384399999999999</v>
+        <v>-4.566</v>
       </c>
       <c r="L10" t="n">
-        <v>8.4437</v>
+        <v>-3.5226</v>
       </c>
       <c r="M10" t="n">
-        <v>-48.1855</v>
+        <v>-2.8126</v>
       </c>
       <c r="N10" t="n">
-        <v>-24.5137</v>
+        <v>-2.7217</v>
       </c>
       <c r="O10" t="n">
-        <v>-23.6719</v>
+        <v>-0.09129999999999994</v>
       </c>
       <c r="P10" t="n">
-        <v>-12.2289</v>
+        <v>-2.2235</v>
       </c>
       <c r="Q10" t="n">
-        <v>-67.81489999999999</v>
+        <v>-7.9672</v>
       </c>
       <c r="R10" t="n">
-        <v>55.5857</v>
+        <v>5.744</v>
       </c>
       <c r="S10" t="n">
-        <v>8.0688</v>
+        <v>-2.0392</v>
       </c>
       <c r="T10" t="n">
-        <v>5.3034</v>
+        <v>-0.9706999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7657</v>
+        <v>-1.0681</v>
       </c>
       <c r="V10" t="n">
-        <v>17.376</v>
+        <v>-8.746599999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>34.2961</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.9195</v>
+        <v>-8.746599999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. HERNANDEZ CASTANO</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>-26.1921</v>
+        <v>-24.3654</v>
       </c>
       <c r="E11" t="n">
-        <v>-17.7668</v>
+        <v>-10.8635</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.425000000000001</v>
+        <v>-13.502</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.9013</v>
+        <v>-17.3425</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.2875</v>
+        <v>-8.144</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.6138</v>
+        <v>-9.198599999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.0885</v>
+        <v>-4.5085</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.566</v>
+        <v>-1.2761</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.5226</v>
+        <v>-3.2322</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8126</v>
+        <v>-12.834</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.7217</v>
+        <v>-6.8678</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.09129999999999994</v>
+        <v>-5.966</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2235</v>
+        <v>4.6322</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.9672</v>
+        <v>-5.1879</v>
       </c>
       <c r="R11" t="n">
-        <v>5.744</v>
+        <v>9.8202</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.3205</v>
+        <v>-2.7181</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.711</v>
+        <v>-0.8512</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6098</v>
+        <v>-1.8667</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.746599999999999</v>
+        <v>-8.9374</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3156</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.746599999999999</v>
+        <v>-8.6218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-27.2428</v>
+        <v>-26.8607</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.4307</v>
+        <v>-20.7368</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.8119</v>
+        <v>-6.1236</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.3425</v>
+        <v>-35.3574</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.144</v>
+        <v>-20.1295</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.198599999999999</v>
+        <v>-15.2282</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.5085</v>
+        <v>12.8279</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2761</v>
+        <v>4.384399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.2322</v>
+        <v>8.4437</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.834</v>
+        <v>-48.1855</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.8678</v>
+        <v>-24.5137</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.966</v>
+        <v>-23.6719</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6322</v>
+        <v>-12.2289</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.1879</v>
+        <v>-67.81489999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>9.8202</v>
+        <v>55.5857</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.5952</v>
+        <v>3.3504</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4186</v>
+        <v>-0.04540000000000025</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1766</v>
+        <v>3.3953</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.9374</v>
+        <v>17.376</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3156</v>
+        <v>34.2961</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.6218</v>
+        <v>-16.9195</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>D. PENAS REINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>-28.7476</v>
+        <v>-27.7209</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.4649</v>
+        <v>-20.622</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.2829</v>
+        <v>-7.0985</v>
       </c>
       <c r="G13" t="n">
-        <v>-19.4062</v>
+        <v>-19.1404</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.8666</v>
+        <v>-7.209000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.5397</v>
+        <v>-11.9313</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.5385</v>
+        <v>-6.9804</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.8973</v>
+        <v>-0.0397000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6411</v>
+        <v>-6.9408</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.8676</v>
+        <v>-12.1601</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.969</v>
+        <v>-7.169499999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.8985</v>
+        <v>-4.9909</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5559000000000003</v>
+        <v>-2.5941</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.5259</v>
+        <v>-14.0818</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9701</v>
+        <v>11.4877</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5491</v>
+        <v>-2.9642</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7140000000000001</v>
+        <v>-0.8162999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8349</v>
+        <v>-2.1476</v>
       </c>
       <c r="V13" t="n">
-        <v>-12.3348</v>
+        <v>-3.022</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8854</v>
+        <v>1.2566</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.2205</v>
+        <v>-4.2786</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.2201</v>
+        <v>-31.3401</v>
       </c>
       <c r="E14" t="n">
-        <v>-38.4289</v>
+        <v>-20.2476</v>
       </c>
       <c r="F14" t="n">
-        <v>8.208600000000001</v>
+        <v>-11.0924</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.6394</v>
+        <v>-19.4062</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4277999999999995</v>
+        <v>-11.8666</v>
       </c>
       <c r="I14" t="n">
-        <v>-31.0676</v>
+        <v>-7.5397</v>
       </c>
       <c r="J14" t="n">
-        <v>3.070500000000001</v>
+        <v>-7.5385</v>
       </c>
       <c r="K14" t="n">
-        <v>21.6488</v>
+        <v>-4.8973</v>
       </c>
       <c r="L14" t="n">
-        <v>-18.5781</v>
+        <v>-2.6411</v>
       </c>
       <c r="M14" t="n">
-        <v>-33.7098</v>
+        <v>-11.8676</v>
       </c>
       <c r="N14" t="n">
-        <v>-21.2204</v>
+        <v>-6.969</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.4893</v>
+        <v>-4.8985</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.337999999999999</v>
+        <v>-0.5559000000000003</v>
       </c>
       <c r="Q14" t="n">
-        <v>-63.1829</v>
+        <v>-13.5259</v>
       </c>
       <c r="R14" t="n">
-        <v>54.8452</v>
+        <v>12.9701</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9582</v>
+        <v>0.9566000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4314</v>
+        <v>-1.0688</v>
       </c>
       <c r="U14" t="n">
-        <v>6.389799999999999</v>
+        <v>2.0255</v>
       </c>
       <c r="V14" t="n">
-        <v>6.798999999999999</v>
+        <v>-12.3348</v>
       </c>
       <c r="W14" t="n">
-        <v>26.1149</v>
+        <v>1.8854</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.3159</v>
+        <v>-14.2205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. PENAS REINO</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-31.0076</v>
+        <v>-31.6966</v>
       </c>
       <c r="E15" t="n">
-        <v>-21.0252</v>
+        <v>-29.6103</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.9824</v>
+        <v>-2.086399999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-19.1404</v>
+        <v>-30.7639</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.209000000000001</v>
+        <v>-21.2554</v>
       </c>
       <c r="I15" t="n">
-        <v>-11.9313</v>
+        <v>-9.5085</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.9804</v>
+        <v>4.577799999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0397000000000001</v>
+        <v>0.2609999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.9408</v>
+        <v>4.316800000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-12.1601</v>
+        <v>-35.342</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.169499999999999</v>
+        <v>-21.5166</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.9909</v>
+        <v>-13.8252</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.5941</v>
+        <v>-5.5586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.0818</v>
+        <v>-56.5124</v>
       </c>
       <c r="R15" t="n">
-        <v>11.4877</v>
+        <v>50.9541</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.2512</v>
+        <v>10.793</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2198</v>
+        <v>4.395700000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.0316</v>
+        <v>6.3972</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.022</v>
+        <v>-6.167</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2566</v>
+        <v>17.9288</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.2786</v>
+        <v>-24.0955</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.4436</v>
+        <v>-31.9039</v>
       </c>
       <c r="E16" t="n">
-        <v>-28.61</v>
+        <v>-37.2826</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8336</v>
+        <v>5.3788</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.3469</v>
+        <v>-30.6394</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.0411</v>
+        <v>0.4277999999999995</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6939</v>
+        <v>-31.0676</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3044</v>
+        <v>3.070500000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.634500000000001</v>
+        <v>21.6488</v>
       </c>
       <c r="L16" t="n">
-        <v>6.938800000000001</v>
+        <v>-18.5781</v>
       </c>
       <c r="M16" t="n">
-        <v>-13.6513</v>
+        <v>-33.7098</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.4063</v>
+        <v>-21.2204</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.245</v>
+        <v>-12.4893</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.7056</v>
+        <v>-8.337999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-25.199</v>
+        <v>-63.1829</v>
       </c>
       <c r="R16" t="n">
-        <v>21.4936</v>
+        <v>54.8452</v>
       </c>
       <c r="S16" t="n">
-        <v>-15.8035</v>
+        <v>0.2742999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.601</v>
+        <v>-3.285</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.2025</v>
+        <v>3.5595</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.5877</v>
+        <v>6.798999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8853</v>
+        <v>26.1149</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.473199999999999</v>
+        <v>-19.3159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-42.2282</v>
+        <v>-33.6943</v>
       </c>
       <c r="E17" t="n">
-        <v>-26.298</v>
+        <v>-39.9605</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.9302</v>
+        <v>6.2663</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.4604</v>
+        <v>-11.0857</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4877000000000001</v>
+        <v>-10.6307</v>
       </c>
       <c r="I17" t="n">
-        <v>-15.9479</v>
+        <v>-0.4551000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>9.2049</v>
+        <v>-0.9257000000000009</v>
       </c>
       <c r="K17" t="n">
-        <v>12.9521</v>
+        <v>-0.7137999999999998</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.747000000000001</v>
+        <v>-0.2118999999999995</v>
       </c>
       <c r="M17" t="n">
-        <v>-24.6652</v>
+        <v>-10.1599</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.4643</v>
+        <v>-9.9169</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.2008</v>
+        <v>-0.2434</v>
       </c>
       <c r="P17" t="n">
-        <v>-20.3817</v>
+        <v>-25.199</v>
       </c>
       <c r="Q17" t="n">
-        <v>-41.319</v>
+        <v>-43.7277</v>
       </c>
       <c r="R17" t="n">
-        <v>20.9375</v>
+        <v>18.5286</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.7966</v>
+        <v>-4.6495</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.285299999999999</v>
+        <v>-2.5437</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.5115</v>
+        <v>-2.1057</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4104</v>
+        <v>7.2398</v>
       </c>
       <c r="W17" t="n">
-        <v>15.1013</v>
+        <v>7.236599999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-9.690899999999999</v>
+        <v>0.003299999999999859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>-42.8938</v>
+        <v>-35.4638</v>
       </c>
       <c r="E18" t="n">
-        <v>-44.7275</v>
+        <v>-22.6517</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8335</v>
+        <v>-12.8124</v>
       </c>
       <c r="G18" t="n">
-        <v>-11.0857</v>
+        <v>-15.4604</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.6307</v>
+        <v>0.4877000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4551000000000001</v>
+        <v>-15.9479</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9257000000000009</v>
+        <v>9.2049</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7137999999999998</v>
+        <v>12.9521</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2118999999999995</v>
+        <v>-3.747000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-10.1599</v>
+        <v>-24.6652</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.9169</v>
+        <v>-12.4643</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2434</v>
+        <v>-12.2008</v>
       </c>
       <c r="P18" t="n">
-        <v>-25.199</v>
+        <v>-20.3817</v>
       </c>
       <c r="Q18" t="n">
-        <v>-43.7277</v>
+        <v>-41.319</v>
       </c>
       <c r="R18" t="n">
-        <v>18.5286</v>
+        <v>20.9375</v>
       </c>
       <c r="S18" t="n">
-        <v>-13.8487</v>
+        <v>-5.0323</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.3104</v>
+        <v>-5.6389</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.538399999999999</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2398</v>
+        <v>5.4104</v>
       </c>
       <c r="W18" t="n">
-        <v>7.236599999999999</v>
+        <v>15.1013</v>
       </c>
       <c r="X18" t="n">
-        <v>0.003299999999999859</v>
+        <v>-9.690899999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-50.6869</v>
+        <v>-48.4794</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.0981</v>
+        <v>-40.6557</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.5888</v>
+        <v>-7.824</v>
       </c>
       <c r="G19" t="n">
-        <v>-36.6627</v>
+        <v>-42.1541</v>
       </c>
       <c r="H19" t="n">
-        <v>-14.8364</v>
+        <v>-24.0429</v>
       </c>
       <c r="I19" t="n">
-        <v>-21.8263</v>
+        <v>-18.111</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.714600000000001</v>
+        <v>-16.1531</v>
       </c>
       <c r="K19" t="n">
-        <v>2.482200000000001</v>
+        <v>-5.6335</v>
       </c>
       <c r="L19" t="n">
-        <v>-9.1965</v>
+        <v>-10.5196</v>
       </c>
       <c r="M19" t="n">
-        <v>-29.9482</v>
+        <v>-26.001</v>
       </c>
       <c r="N19" t="n">
-        <v>-17.3185</v>
+        <v>-18.4094</v>
       </c>
       <c r="O19" t="n">
-        <v>-12.6298</v>
+        <v>-7.5914</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.7437</v>
+        <v>12.7848</v>
       </c>
       <c r="Q19" t="n">
-        <v>-39.2809</v>
+        <v>-22.4196</v>
       </c>
       <c r="R19" t="n">
-        <v>33.5368</v>
+        <v>35.2044</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3599</v>
+        <v>-8.099</v>
       </c>
       <c r="T19" t="n">
-        <v>4.9398</v>
+        <v>-5.228</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.2999</v>
+        <v>-2.8705</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.9205</v>
+        <v>-11.0119</v>
       </c>
       <c r="W19" t="n">
-        <v>11.9575</v>
+        <v>3.1455</v>
       </c>
       <c r="X19" t="n">
-        <v>-18.878</v>
+        <v>-14.1573</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-64.14149999999999</v>
+        <v>-50.7205</v>
       </c>
       <c r="E20" t="n">
-        <v>-48.602</v>
+        <v>-32.6092</v>
       </c>
       <c r="F20" t="n">
-        <v>-15.5397</v>
+        <v>-18.111</v>
       </c>
       <c r="G20" t="n">
-        <v>-42.1541</v>
+        <v>-36.6627</v>
       </c>
       <c r="H20" t="n">
-        <v>-24.0429</v>
+        <v>-14.8364</v>
       </c>
       <c r="I20" t="n">
-        <v>-18.111</v>
+        <v>-21.8263</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.1531</v>
+        <v>-6.714600000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.6335</v>
+        <v>2.482200000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-10.5196</v>
+        <v>-9.1965</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.001</v>
+        <v>-29.9482</v>
       </c>
       <c r="N20" t="n">
-        <v>-18.4094</v>
+        <v>-17.3185</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.5914</v>
+        <v>-12.6298</v>
       </c>
       <c r="P20" t="n">
-        <v>12.7848</v>
+        <v>-5.7437</v>
       </c>
       <c r="Q20" t="n">
-        <v>-22.4196</v>
+        <v>-39.2809</v>
       </c>
       <c r="R20" t="n">
-        <v>35.2044</v>
+        <v>33.5368</v>
       </c>
       <c r="S20" t="n">
-        <v>-23.7608</v>
+        <v>-1.3935</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.1749</v>
+        <v>1.4288</v>
       </c>
       <c r="U20" t="n">
-        <v>-10.5859</v>
+        <v>-2.8221</v>
       </c>
       <c r="V20" t="n">
-        <v>-11.0119</v>
+        <v>-6.9205</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1455</v>
+        <v>11.9575</v>
       </c>
       <c r="X20" t="n">
-        <v>-14.1573</v>
+        <v>-18.878</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-424.8271</v>
+        <v>-397.8116</v>
       </c>
       <c r="E21" t="n">
-        <v>-319.0552999999999</v>
+        <v>-313.5836</v>
       </c>
       <c r="F21" t="n">
-        <v>-105.7723</v>
+        <v>-84.2276</v>
       </c>
       <c r="G21" t="n">
         <v>-288.8544</v>
@@ -2068,7 +2068,7 @@
         <v>-0.1729000000000021</v>
       </c>
       <c r="K21" t="n">
-        <v>47.98179999999999</v>
+        <v>47.9818</v>
       </c>
       <c r="L21" t="n">
         <v>-48.1536</v>
@@ -2092,13 +2092,13 @@
         <v>363.1627</v>
       </c>
       <c r="S21" t="n">
-        <v>-49.1997</v>
+        <v>-22.1847</v>
       </c>
       <c r="T21" t="n">
-        <v>-27.8129</v>
+        <v>-22.3401</v>
       </c>
       <c r="U21" t="n">
-        <v>-21.3875</v>
+        <v>0.1563000000000003</v>
       </c>
       <c r="V21" t="n">
         <v>-17.2907</v>
